--- a/public/template_excel/bu_quet_mat.xlsx
+++ b/public/template_excel/bu_quet_mat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\FESP\fe-service-portal\public\template_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F21F4E-F38D-4AEA-A4E2-759D6854C58E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2BA97D-AD8E-46AC-8C8F-A2CD24EC7A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="745">
   <si>
     <t>stt</t>
   </si>
@@ -2261,6 +2261,9 @@
   </si>
   <si>
     <t>2026-2-14</t>
+  </si>
+  <si>
+    <t>B1</t>
   </si>
 </sst>
 </file>
@@ -3680,7 +3683,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3729,9 +3732,6 @@
     <xf numFmtId="0" fontId="73" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="71" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="366">
     <cellStyle name="??" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4926,18 +4926,17 @@
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="22" t="s">
         <v>674</v>
       </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="5" t="s">
         <v>743</v>
       </c>
-      <c r="E4" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>10</v>
+      <c r="E4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>744</v>
       </c>
     </row>
     <row r="5" spans="1:11">
